--- a/data/trans_orig/P24F-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P24F-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2007</t>
+          <t>Población según si le gustaría dejar de fumar en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29029</t>
+          <t>29093</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51371</t>
+          <t>50755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38073</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54943</t>
+          <t>54510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82781</t>
+          <t>82201</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69789</t>
+          <t>69262</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92585</t>
+          <t>93551</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30526</t>
+          <t>30339</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49545</t>
+          <t>49783</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>106760</t>
+          <t>106855</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>136617</t>
+          <t>138281</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39110</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32809</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57354</t>
+          <t>58164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18260</t>
+          <t>18572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46540</t>
+          <t>47061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70158</t>
+          <t>71809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39144</t>
+          <t>37655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59700</t>
+          <t>60176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91933</t>
+          <t>91795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123736</t>
+          <t>123114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65497</t>
+          <t>65711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42842</t>
+          <t>42309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65164</t>
+          <t>65111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91834</t>
+          <t>92061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123883</t>
+          <t>122776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,78%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29664</t>
+          <t>29428</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>15823</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33759</t>
+          <t>33717</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31700</t>
+          <t>32289</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55947</t>
+          <t>56946</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20798</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>8275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26431</t>
+          <t>25726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80648</t>
+          <t>79702</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>112543</t>
+          <t>110533</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21930</t>
+          <t>22230</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>94769</t>
+          <t>93372</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>127858</t>
+          <t>127274</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90643</t>
+          <t>91787</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122958</t>
+          <t>124132</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>12383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>25065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108311</t>
+          <t>107545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141940</t>
+          <t>142628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,35%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>28980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52975</t>
+          <t>53604</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37877</t>
+          <t>38253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64380</t>
+          <t>66349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35640</t>
+          <t>33426</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22611</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45914</t>
+          <t>45126</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>173141</t>
+          <t>171395</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>217963</t>
+          <t>215939</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69650</t>
+          <t>70504</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100101</t>
+          <t>101127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>250826</t>
+          <t>251626</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>306009</t>
+          <t>305877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>200088</t>
+          <t>201078</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>246063</t>
+          <t>247405</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96637</t>
+          <t>95790</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>129189</t>
+          <t>125988</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>307174</t>
+          <t>308431</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>367089</t>
+          <t>365302</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102848</t>
+          <t>103454</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>142074</t>
+          <t>144708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26282</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47677</t>
+          <t>49421</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135780</t>
+          <t>135410</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>181103</t>
+          <t>184843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14888</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27058</t>
+          <t>27990</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61014</t>
+          <t>59729</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88042</t>
+          <t>87885</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52483</t>
+          <t>52496</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78554</t>
+          <t>77727</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118065</t>
+          <t>119858</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>156883</t>
+          <t>158762</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,23%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51408</t>
+          <t>51634</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77869</t>
+          <t>79548</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62081</t>
+          <t>62436</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89898</t>
+          <t>90189</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>121267</t>
+          <t>120593</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>159504</t>
+          <t>158894</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30506</t>
+          <t>30719</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>54304</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>21001</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41659</t>
+          <t>41764</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>57091</t>
+          <t>56001</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>87382</t>
+          <t>88648</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10865</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20750</t>
+          <t>21436</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>26356</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47085</t>
+          <t>46477</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>65186</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>46156</t>
+          <t>48139</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>71057</t>
+          <t>70667</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>101239</t>
+          <t>98761</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>132144</t>
+          <t>130165</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>49079</t>
+          <t>49291</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>74706</t>
+          <t>73756</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>54090</t>
+          <t>53972</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>82417</t>
+          <t>83944</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>27583</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25625</t>
+          <t>26442</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48323</t>
+          <t>47729</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>42481</t>
+          <t>43892</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>69544</t>
+          <t>70423</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>43428</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>71803</t>
+          <t>74007</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>34865</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>61873</t>
+          <t>61319</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>84556</t>
+          <t>84798</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>124293</t>
+          <t>125726</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>484908</t>
+          <t>481831</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>557874</t>
+          <t>553768</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>275306</t>
+          <t>275889</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>332063</t>
+          <t>330825</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>776293</t>
+          <t>776366</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>867153</t>
+          <t>863856</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>501151</t>
+          <t>501197</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>572813</t>
+          <t>572687</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>330011</t>
+          <t>331826</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>388361</t>
+          <t>389552</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>849803</t>
+          <t>848537</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>941419</t>
+          <t>940099</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>239575</t>
+          <t>241593</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>298034</t>
+          <t>300018</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>133997</t>
+          <t>133301</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>179140</t>
+          <t>178772</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>382427</t>
+          <t>386896</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>460419</t>
+          <t>458932</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2012</t>
+          <t>Población según si le gustaría dejar de fumar en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29659</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25711</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49331</t>
+          <t>48441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82446</t>
+          <t>81566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106369</t>
+          <t>106793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53976</t>
+          <t>54517</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73746</t>
+          <t>73831</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>142059</t>
+          <t>141928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172642</t>
+          <t>174734</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18640</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38446</t>
+          <t>40280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25204</t>
+          <t>25404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32987</t>
+          <t>33201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56339</t>
+          <t>59052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>17368</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28649</t>
+          <t>30275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16783</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41462</t>
+          <t>40172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76533</t>
+          <t>77638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104183</t>
+          <t>103688</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75540</t>
+          <t>75382</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97235</t>
+          <t>96874</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160272</t>
+          <t>160125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194295</t>
+          <t>193956</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,23%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21846</t>
+          <t>23171</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>45079</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18074</t>
+          <t>18042</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37308</t>
+          <t>38174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46903</t>
+          <t>44635</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77125</t>
+          <t>74749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6122,62 +6122,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4540</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4642</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48686</t>
+          <t>49169</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23514</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6250,47 +6250,47 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>51774</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>38910</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>65549</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>11,06%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>28,25%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>51774</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>39233</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>66338</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>14,72%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174922</t>
+          <t>172457</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204980</t>
+          <t>202979</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41404</t>
+          <t>43421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>59987</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>222621</t>
+          <t>223025</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>258311</t>
+          <t>259216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,7%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30598</t>
+          <t>31268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55674</t>
+          <t>55298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>24616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45206</t>
+          <t>45913</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74331</t>
+          <t>73024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56228</t>
+          <t>56470</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90326</t>
+          <t>90342</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36152</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61626</t>
+          <t>61659</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>95258</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>140029</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>298210</t>
+          <t>297140</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>342917</t>
+          <t>340563</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>156864</t>
+          <t>156176</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>191094</t>
+          <t>191282</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>464872</t>
+          <t>467123</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>522807</t>
+          <t>522833</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87773</t>
+          <t>88108</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124382</t>
+          <t>124420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45713</t>
+          <t>46212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74382</t>
+          <t>73822</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>143012</t>
+          <t>139197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>188471</t>
+          <t>187274</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>917</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36519</t>
+          <t>34973</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62230</t>
+          <t>60928</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>21893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42038</t>
+          <t>43983</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62980</t>
+          <t>62890</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>98271</t>
+          <t>96778</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>106266</t>
+          <t>105903</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>136171</t>
+          <t>134919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>134731</t>
+          <t>133750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163803</t>
+          <t>163126</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>249448</t>
+          <t>248368</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>290554</t>
+          <t>289649</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>61718</t>
+          <t>60178</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>23628</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>43968</t>
+          <t>44990</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>64968</t>
+          <t>66440</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>97270</t>
+          <t>98661</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8809</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -7907,12 +7907,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11375</t>
+          <t>10529</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25030</t>
+          <t>24601</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7922,12 +7922,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>16424</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>36269</t>
+          <t>35789</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31129</t>
+          <t>31519</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55735</t>
+          <t>54944</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -8020,12 +8020,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7234</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>74565</t>
+          <t>74209</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>98019</t>
+          <t>100641</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>84432</t>
+          <t>85679</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>114890</t>
+          <t>114716</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -8133,12 +8133,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>37444</t>
+          <t>38254</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37994</t>
+          <t>35964</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>61579</t>
+          <t>60654</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>64924</t>
+          <t>63067</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>94211</t>
+          <t>92580</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,04%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>14260</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>32594</t>
+          <t>32651</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>25656</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48338</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -8476,12 +8476,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>186039</t>
+          <t>184723</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>240017</t>
+          <t>240198</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>122476</t>
+          <t>121190</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>168479</t>
+          <t>166850</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>320662</t>
+          <t>323560</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>393197</t>
+          <t>395870</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>792211</t>
+          <t>786863</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>865155</t>
+          <t>863745</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>584472</t>
+          <t>579761</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>645603</t>
+          <t>640885</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1392760</t>
+          <t>1391376</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1490352</t>
+          <t>1490155</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>256524</t>
+          <t>255100</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>316913</t>
+          <t>318641</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>174832</t>
+          <t>176940</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>225753</t>
+          <t>227753</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>445135</t>
+          <t>445229</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>527620</t>
+          <t>523732</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2016</t>
+          <t>Población según si le gustaría dejar de fumar en 2016 (tasa de respuesta: 98,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29799</t>
+          <t>29746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>20268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42647</t>
+          <t>42260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56189</t>
+          <t>57124</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76292</t>
+          <t>76596</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37172</t>
+          <t>36989</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51928</t>
+          <t>51853</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>97333</t>
+          <t>97477</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>122914</t>
+          <t>123958</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22626</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>18580</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37529</t>
+          <t>37322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9735,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>911</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12058</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9848,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>9829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26041</t>
+          <t>26366</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23766</t>
+          <t>25508</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46989</t>
+          <t>47865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50576</t>
+          <t>51837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71575</t>
+          <t>71536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48367</t>
+          <t>48604</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68504</t>
+          <t>68766</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105044</t>
+          <t>103885</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134459</t>
+          <t>133651</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,62%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>32216</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28962</t>
+          <t>28791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33508</t>
+          <t>31756</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57027</t>
+          <t>57017</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32315</t>
+          <t>30207</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55479</t>
+          <t>53764</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>11633</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>36300</t>
+          <t>34502</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61054</t>
+          <t>62377</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -10530,12 +10530,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111780</t>
+          <t>111396</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140570</t>
+          <t>142084</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10545,12 +10545,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31239</t>
+          <t>31296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44595</t>
+          <t>44440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10580,12 +10580,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148418</t>
+          <t>148545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181091</t>
+          <t>182406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10643,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>28753</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52827</t>
+          <t>53072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36163</t>
+          <t>34871</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61304</t>
+          <t>60211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24085</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72542</t>
+          <t>71501</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>106837</t>
+          <t>105081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60514</t>
+          <t>60705</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90350</t>
+          <t>90846</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142030</t>
+          <t>142530</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>188653</t>
+          <t>187531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11071,12 +11071,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -11099,12 +11099,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>214118</t>
+          <t>214452</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>254741</t>
+          <t>255058</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>161489</t>
+          <t>161967</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>195178</t>
+          <t>196252</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>387805</t>
+          <t>386689</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>439367</t>
+          <t>442582</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11184,12 +11184,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -11212,12 +11212,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75558</t>
+          <t>75979</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>110966</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40772</t>
+          <t>40807</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67704</t>
+          <t>66724</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123836</t>
+          <t>123610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166620</t>
+          <t>165064</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16798</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23496</t>
+          <t>24224</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11555,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29903</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53116</t>
+          <t>54137</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29037</t>
+          <t>28477</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50901</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63947</t>
+          <t>64003</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97770</t>
+          <t>96564</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11640,12 +11640,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113660</t>
+          <t>114380</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>147120</t>
+          <t>146605</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101601</t>
+          <t>101148</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130419</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11738,12 +11738,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>224806</t>
+          <t>226127</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>266932</t>
+          <t>267997</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,14%</t>
         </is>
       </c>
     </row>
@@ -11781,12 +11781,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>46025</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>72700</t>
+          <t>73731</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>38883</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>66018</t>
+          <t>65783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>94179</t>
+          <t>93789</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>133481</t>
+          <t>131238</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -12011,12 +12011,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12061,12 +12061,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>15995</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12096,12 +12096,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29025</t>
+          <t>28294</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12139,12 +12139,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27857</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49704</t>
+          <t>49715</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45453</t>
+          <t>46030</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>72667</t>
+          <t>72230</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -12237,12 +12237,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16987</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32713</t>
+          <t>32495</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12252,12 +12252,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>71672</t>
+          <t>72069</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>98861</t>
+          <t>98373</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12287,12 +12287,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>92797</t>
+          <t>93008</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>124472</t>
+          <t>124945</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -12350,12 +12350,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>32035</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12385,12 +12385,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>30874</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>54534</t>
+          <t>53887</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12400,12 +12400,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>51358</t>
+          <t>51717</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>78449</t>
+          <t>79601</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -12580,12 +12580,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>22028</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>45701</t>
+          <t>44862</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>41100</t>
+          <t>41349</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>71474</t>
+          <t>70183</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12693,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>202029</t>
+          <t>202210</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>258233</t>
+          <t>259164</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>158616</t>
+          <t>159086</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>208637</t>
+          <t>208274</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12763,12 +12763,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>372703</t>
+          <t>379401</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>445503</t>
+          <t>452894</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12778,12 +12778,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -12806,12 +12806,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>609818</t>
+          <t>608660</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>684459</t>
+          <t>679223</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12821,12 +12821,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>491422</t>
+          <t>491200</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>551755</t>
+          <t>551729</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1122461</t>
+          <t>1123654</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1213819</t>
+          <t>1214793</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,64%</t>
         </is>
       </c>
     </row>
@@ -12919,12 +12919,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>224715</t>
+          <t>224513</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>280392</t>
+          <t>280979</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>159466</t>
+          <t>162480</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>212258</t>
+          <t>210310</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12969,12 +12969,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12989,12 +12989,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>401698</t>
+          <t>400763</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>474643</t>
+          <t>474357</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13004,12 +13004,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24F-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P24F-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29093</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>50396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>20485</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38641</t>
+          <t>38249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54510</t>
+          <t>55187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82201</t>
+          <t>83897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69262</t>
+          <t>69337</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93551</t>
+          <t>93927</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>31513</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49783</t>
+          <t>50006</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>106855</t>
+          <t>106256</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>138281</t>
+          <t>137926</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,55%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18551</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38593</t>
+          <t>37172</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25736</t>
+          <t>25505</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33801</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58164</t>
+          <t>58021</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47061</t>
+          <t>48150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71809</t>
+          <t>71219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37655</t>
+          <t>37442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60176</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91795</t>
+          <t>91896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123114</t>
+          <t>125107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41573</t>
+          <t>41822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65711</t>
+          <t>65277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42309</t>
+          <t>43609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65111</t>
+          <t>65457</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92061</t>
+          <t>89795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122776</t>
+          <t>121589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>11964</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>28394</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15823</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33717</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32289</t>
+          <t>32173</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56946</t>
+          <t>56824</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25726</t>
+          <t>25016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79702</t>
+          <t>80872</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>110533</t>
+          <t>110645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22230</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>93372</t>
+          <t>95320</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>127274</t>
+          <t>127541</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91787</t>
+          <t>93078</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124132</t>
+          <t>123909</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25065</t>
+          <t>24971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107545</t>
+          <t>108668</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142628</t>
+          <t>144177</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,86%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28980</t>
+          <t>29459</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53604</t>
+          <t>53481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16422</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38253</t>
+          <t>38805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66349</t>
+          <t>64106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33426</t>
+          <t>35666</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>15866</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23225</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45126</t>
+          <t>45450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>171395</t>
+          <t>173275</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>215939</t>
+          <t>217270</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70504</t>
+          <t>69494</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101127</t>
+          <t>99449</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>251626</t>
+          <t>251107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305877</t>
+          <t>304330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>201078</t>
+          <t>201940</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>247405</t>
+          <t>248370</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95790</t>
+          <t>95388</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>125988</t>
+          <t>128621</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>308431</t>
+          <t>307940</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>365302</t>
+          <t>362269</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103454</t>
+          <t>103029</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144708</t>
+          <t>142564</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26933</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49421</t>
+          <t>49367</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135410</t>
+          <t>134126</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>184843</t>
+          <t>179752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>16182</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27990</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59729</t>
+          <t>60276</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87885</t>
+          <t>88710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52496</t>
+          <t>51946</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77727</t>
+          <t>77295</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>119858</t>
+          <t>118541</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158762</t>
+          <t>158606</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51634</t>
+          <t>50663</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>79548</t>
+          <t>76388</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62436</t>
+          <t>61984</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90189</t>
+          <t>89600</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>120593</t>
+          <t>119463</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>158894</t>
+          <t>158424</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30719</t>
+          <t>30722</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54304</t>
+          <t>55124</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>21001</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41764</t>
+          <t>41137</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>56001</t>
+          <t>57425</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>88648</t>
+          <t>88098</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>20634</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10778</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26356</t>
+          <t>27906</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46477</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65186</t>
+          <t>64419</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>48139</t>
+          <t>47294</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70667</t>
+          <t>71483</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>98761</t>
+          <t>99387</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>130165</t>
+          <t>129985</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,6%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>49291</t>
+          <t>48627</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>73756</t>
+          <t>73301</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>53972</t>
+          <t>56824</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>83944</t>
+          <t>83604</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11982</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>28273</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26442</t>
+          <t>26627</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>47729</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43892</t>
+          <t>42775</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>70423</t>
+          <t>70258</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>43428</t>
+          <t>42272</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>74007</t>
+          <t>72967</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>35318</t>
+          <t>34362</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>61319</t>
+          <t>61549</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>84798</t>
+          <t>83575</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>125726</t>
+          <t>123571</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>481831</t>
+          <t>483116</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>553768</t>
+          <t>551490</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>275889</t>
+          <t>276736</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>330825</t>
+          <t>331124</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>776366</t>
+          <t>771343</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>863856</t>
+          <t>863501</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>501197</t>
+          <t>500479</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>572687</t>
+          <t>573895</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>331826</t>
+          <t>329363</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>389552</t>
+          <t>386724</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>848537</t>
+          <t>850895</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>940099</t>
+          <t>940957</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,97%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>241593</t>
+          <t>239637</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>300018</t>
+          <t>299365</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>133301</t>
+          <t>132037</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>178772</t>
+          <t>178106</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>386896</t>
+          <t>386576</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>458932</t>
+          <t>461314</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25753</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>25481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48441</t>
+          <t>50055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81566</t>
+          <t>81818</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106793</t>
+          <t>105922</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54517</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73831</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141928</t>
+          <t>138977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>174734</t>
+          <t>172364</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,25%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40280</t>
+          <t>37582</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25404</t>
+          <t>25923</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33201</t>
+          <t>32558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59052</t>
+          <t>58508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>12883</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30275</t>
+          <t>29453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17526</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40172</t>
+          <t>42331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77638</t>
+          <t>77399</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103688</t>
+          <t>103629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5759,47 +5759,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>68,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>86620</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>74059</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>97866</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>68,91%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86620</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75382</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>96874</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>68,91%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160125</t>
+          <t>159887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193956</t>
+          <t>195161</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45079</t>
+          <t>44915</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18042</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>39319</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44635</t>
+          <t>46104</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74749</t>
+          <t>76245</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26921</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49169</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>38910</t>
+          <t>39111</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>65549</t>
+          <t>66067</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>172457</t>
+          <t>173777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202979</t>
+          <t>204795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43421</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59987</t>
+          <t>59138</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>223025</t>
+          <t>222234</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>259216</t>
+          <t>256369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>72,89%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31268</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55298</t>
+          <t>54857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>24332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45913</t>
+          <t>45052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73024</t>
+          <t>72879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>17904</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56470</t>
+          <t>57323</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90342</t>
+          <t>91722</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>35251</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61659</t>
+          <t>61803</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95258</t>
+          <t>97988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>140029</t>
+          <t>140781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>297140</t>
+          <t>296809</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>340563</t>
+          <t>339976</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>156176</t>
+          <t>156799</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>191282</t>
+          <t>191151</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>467123</t>
+          <t>465391</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>522833</t>
+          <t>521823</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,45%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>88108</t>
+          <t>85915</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124420</t>
+          <t>122569</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46212</t>
+          <t>44660</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73822</t>
+          <t>74324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139197</t>
+          <t>139893</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>187274</t>
+          <t>187156</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8744</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60928</t>
+          <t>61592</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>21486</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43983</t>
+          <t>43514</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62890</t>
+          <t>63962</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96778</t>
+          <t>97125</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105903</t>
+          <t>103709</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134919</t>
+          <t>134642</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>133750</t>
+          <t>134461</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163126</t>
+          <t>163694</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>248368</t>
+          <t>249256</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>289649</t>
+          <t>292361</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>35828</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60178</t>
+          <t>60650</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>23628</t>
+          <t>22703</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>44990</t>
+          <t>44015</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>66440</t>
+          <t>65511</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>98661</t>
+          <t>98305</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>12764</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -7907,12 +7907,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>11395</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24601</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7922,12 +7922,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35789</t>
+          <t>34654</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31519</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54944</t>
+          <t>54607</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -8020,12 +8020,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>74209</t>
+          <t>73628</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>100641</t>
+          <t>98897</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>85679</t>
+          <t>83588</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>114716</t>
+          <t>113134</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -8133,12 +8133,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>37600</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>35964</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>60654</t>
+          <t>61759</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>63067</t>
+          <t>63481</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>92580</t>
+          <t>92565</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14260</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>32651</t>
+          <t>32381</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22505</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>25656</t>
+          <t>25255</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48848</t>
+          <t>48834</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>184723</t>
+          <t>184907</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>240198</t>
+          <t>242790</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>121190</t>
+          <t>123077</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>166850</t>
+          <t>168070</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>323560</t>
+          <t>322927</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>395870</t>
+          <t>395609</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>786863</t>
+          <t>792585</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>863745</t>
+          <t>864747</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>579761</t>
+          <t>581654</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>640885</t>
+          <t>641438</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1391376</t>
+          <t>1393421</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1490155</t>
+          <t>1494398</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -8702,12 +8702,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>255100</t>
+          <t>253791</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>318641</t>
+          <t>315881</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>176940</t>
+          <t>174113</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>227753</t>
+          <t>227543</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>445229</t>
+          <t>444266</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>523732</t>
+          <t>525650</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10028</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29746</t>
+          <t>30113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15713</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20268</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42260</t>
+          <t>41176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57124</t>
+          <t>55762</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76596</t>
+          <t>76536</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36989</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>52976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>97477</t>
+          <t>97333</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>123958</t>
+          <t>123732</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,09%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>18817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18067</t>
+          <t>17788</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37322</t>
+          <t>37744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9735,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9848,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26913</t>
+          <t>26178</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26366</t>
+          <t>25632</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>24345</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>45906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51837</t>
+          <t>50594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71536</t>
+          <t>70910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48604</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68766</t>
+          <t>68296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103885</t>
+          <t>106564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133651</t>
+          <t>135244</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,4%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32216</t>
+          <t>32516</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12835</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28791</t>
+          <t>28706</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31756</t>
+          <t>31569</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57017</t>
+          <t>54771</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>12186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>30734</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53764</t>
+          <t>55920</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>34502</t>
+          <t>34105</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>62377</t>
+          <t>61680</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -10530,12 +10530,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111396</t>
+          <t>110102</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142084</t>
+          <t>140416</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10545,12 +10545,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31296</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44440</t>
+          <t>44137</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10580,12 +10580,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148545</t>
+          <t>148486</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>182406</t>
+          <t>180957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,72%</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10643,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28753</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53072</t>
+          <t>52355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>35599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60211</t>
+          <t>62423</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15227</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>24527</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71501</t>
+          <t>72132</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105081</t>
+          <t>106497</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60705</t>
+          <t>61262</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90846</t>
+          <t>94650</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142530</t>
+          <t>142406</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>187531</t>
+          <t>188147</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11071,12 +11071,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -11099,12 +11099,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>214452</t>
+          <t>215619</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>255058</t>
+          <t>256663</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>161967</t>
+          <t>161300</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>196252</t>
+          <t>195959</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>386689</t>
+          <t>385817</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>442582</t>
+          <t>441260</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11184,12 +11184,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,87%</t>
         </is>
       </c>
     </row>
@@ -11212,12 +11212,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75979</t>
+          <t>73519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112191</t>
+          <t>108283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40807</t>
+          <t>41058</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66724</t>
+          <t>66789</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123610</t>
+          <t>123075</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165064</t>
+          <t>164418</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>16491</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11555,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>29515</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54137</t>
+          <t>53556</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28477</t>
+          <t>28417</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50957</t>
+          <t>51045</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64003</t>
+          <t>64676</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96564</t>
+          <t>97549</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11640,12 +11640,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114380</t>
+          <t>115528</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>146605</t>
+          <t>146826</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101148</t>
+          <t>101700</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>130419</t>
+          <t>130216</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11738,12 +11738,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>226127</t>
+          <t>224749</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>267997</t>
+          <t>269330</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -11781,12 +11781,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>46025</t>
+          <t>46334</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>73731</t>
+          <t>72685</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38883</t>
+          <t>40615</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65783</t>
+          <t>67712</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>93789</t>
+          <t>93689</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>131238</t>
+          <t>131620</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -11991,7 +11991,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12011,12 +12011,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9479</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>10138</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12061,12 +12061,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12096,12 +12096,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13146</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28294</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12139,12 +12139,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28264</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49715</t>
+          <t>48210</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>46030</t>
+          <t>45130</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>72230</t>
+          <t>71346</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -12237,12 +12237,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32495</t>
+          <t>31898</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12252,12 +12252,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>72069</t>
+          <t>70701</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>98373</t>
+          <t>97538</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12287,12 +12287,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>93008</t>
+          <t>93037</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>124945</t>
+          <t>124165</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -12350,12 +12350,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12385,12 +12385,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>53887</t>
+          <t>54550</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12400,12 +12400,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>51717</t>
+          <t>50501</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>79601</t>
+          <t>78266</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -12580,12 +12580,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>21789</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>44862</t>
+          <t>46160</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>33681</t>
+          <t>34599</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>41349</t>
+          <t>41935</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>70183</t>
+          <t>70698</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12693,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>202210</t>
+          <t>202317</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>259164</t>
+          <t>261038</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>159086</t>
+          <t>160201</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>208035</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12763,12 +12763,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>379401</t>
+          <t>374817</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>452894</t>
+          <t>451207</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12778,12 +12778,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -12806,12 +12806,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>608660</t>
+          <t>611974</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>679223</t>
+          <t>679740</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12821,12 +12821,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>491200</t>
+          <t>490928</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>551729</t>
+          <t>552543</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1123654</t>
+          <t>1120138</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1214793</t>
+          <t>1214580</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -12919,12 +12919,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>224513</t>
+          <t>222332</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>280979</t>
+          <t>280853</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12934,82 +12934,82 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>19,2%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>24,26%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>185625</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>159183</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>211036</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>23,1%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>436711</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>401780</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>476700</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t>19,39%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>185625</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>162480</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>210310</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>17,78%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>23,02%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>436711</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>400763</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>474357</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>21,08%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>19,35%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
